--- a/workspaces/yzz100407/test_output/sample_data/读数表.xlsx
+++ b/workspaces/yzz100407/test_output/sample_data/读数表.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>星巴克咖啡</t>
+          <t>旧名咖啡</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -860,7 +860,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>星巴克咖啡</t>
+          <t>旧名咖啡</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
